--- a/Data_Analysis/Sensitivity analysis/BEV/sweep_results_bev_G1_task075.xlsx
+++ b/Data_Analysis/Sensitivity analysis/BEV/sweep_results_bev_G1_task075.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -251,6 +251,402 @@
         <v>6.9705102068048115</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>325</v>
+      </c>
+      <c r="B4" s="0">
+        <v>3333</v>
+      </c>
+      <c r="C4" s="0">
+        <v>325</v>
+      </c>
+      <c r="D4" s="0">
+        <v>60.076813342244527</v>
+      </c>
+      <c r="E4" s="0">
+        <v>482.10500000000002</v>
+      </c>
+      <c r="F4" s="0">
+        <v>152.7708531824745</v>
+      </c>
+      <c r="G4" s="0">
+        <v>82388.791974754218</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-8341.3589940651509</v>
+      </c>
+      <c r="I4" s="0">
+        <v>5.2050000000000001</v>
+      </c>
+      <c r="J4" s="0">
+        <v>19.23</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.5050000000000008</v>
+      </c>
+      <c r="L4" s="0">
+        <v>3.4100000000000001</v>
+      </c>
+      <c r="M4" s="0">
+        <v>221.23196724367983</v>
+      </c>
+      <c r="N4" s="0">
+        <v>7.0452838762087007</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>325</v>
+      </c>
+      <c r="B5" s="0">
+        <v>3334</v>
+      </c>
+      <c r="C5" s="0">
+        <v>325</v>
+      </c>
+      <c r="D5" s="0">
+        <v>60.076813342244527</v>
+      </c>
+      <c r="E5" s="0">
+        <v>482.10500000000002</v>
+      </c>
+      <c r="F5" s="0">
+        <v>152.7708531824745</v>
+      </c>
+      <c r="G5" s="0">
+        <v>85566.022143181894</v>
+      </c>
+      <c r="H5" s="0">
+        <v>-8341.3589940651509</v>
+      </c>
+      <c r="I5" s="0">
+        <v>5.2050000000000001</v>
+      </c>
+      <c r="J5" s="0">
+        <v>19.23</v>
+      </c>
+      <c r="K5" s="0">
+        <v>2.5050000000000008</v>
+      </c>
+      <c r="L5" s="0">
+        <v>3.4100000000000001</v>
+      </c>
+      <c r="M5" s="0">
+        <v>221.23196724367983</v>
+      </c>
+      <c r="N5" s="0">
+        <v>7.0452838762087007</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>325</v>
+      </c>
+      <c r="B6" s="0">
+        <v>3335</v>
+      </c>
+      <c r="C6" s="0">
+        <v>325</v>
+      </c>
+      <c r="D6" s="0">
+        <v>60.708100565801814</v>
+      </c>
+      <c r="E6" s="0">
+        <v>483.73500000000001</v>
+      </c>
+      <c r="F6" s="0">
+        <v>152.25607444889633</v>
+      </c>
+      <c r="G6" s="0">
+        <v>82276.54722715581</v>
+      </c>
+      <c r="H6" s="0">
+        <v>-8277.649528251537</v>
+      </c>
+      <c r="I6" s="0">
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="J6" s="0">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="K6" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="L6" s="0">
+        <v>3.395</v>
+      </c>
+      <c r="M6" s="0">
+        <v>217.51536773535375</v>
+      </c>
+      <c r="N6" s="0">
+        <v>7.1200340567309111</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>325</v>
+      </c>
+      <c r="B7" s="0">
+        <v>3336</v>
+      </c>
+      <c r="C7" s="0">
+        <v>325</v>
+      </c>
+      <c r="D7" s="0">
+        <v>60.708100565801814</v>
+      </c>
+      <c r="E7" s="0">
+        <v>483.73500000000001</v>
+      </c>
+      <c r="F7" s="0">
+        <v>152.25607444889633</v>
+      </c>
+      <c r="G7" s="0">
+        <v>85296.692381016881</v>
+      </c>
+      <c r="H7" s="0">
+        <v>-8277.649528251537</v>
+      </c>
+      <c r="I7" s="0">
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="J7" s="0">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="K7" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="L7" s="0">
+        <v>3.395</v>
+      </c>
+      <c r="M7" s="0">
+        <v>217.51536773535375</v>
+      </c>
+      <c r="N7" s="0">
+        <v>7.1200340567309111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>325</v>
+      </c>
+      <c r="B8" s="0">
+        <v>3337</v>
+      </c>
+      <c r="C8" s="0">
+        <v>325</v>
+      </c>
+      <c r="D8" s="0">
+        <v>58.713762523220559</v>
+      </c>
+      <c r="E8" s="0">
+        <v>479.23000000000002</v>
+      </c>
+      <c r="F8" s="0">
+        <v>153.68735716365182</v>
+      </c>
+      <c r="G8" s="0">
+        <v>81891.421684389963</v>
+      </c>
+      <c r="H8" s="0">
+        <v>-8480.8981994427359</v>
+      </c>
+      <c r="I8" s="0">
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="J8" s="0">
+        <v>18.18</v>
+      </c>
+      <c r="K8" s="0">
+        <v>2.4350000000000005</v>
+      </c>
+      <c r="L8" s="0">
+        <v>3.3300000000000001</v>
+      </c>
+      <c r="M8" s="0">
+        <v>225.33371016537902</v>
+      </c>
+      <c r="N8" s="0">
+        <v>6.9702760771831391</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>325</v>
+      </c>
+      <c r="B9" s="0">
+        <v>3338</v>
+      </c>
+      <c r="C9" s="0">
+        <v>325</v>
+      </c>
+      <c r="D9" s="0">
+        <v>58.713762523220559</v>
+      </c>
+      <c r="E9" s="0">
+        <v>479.23000000000002</v>
+      </c>
+      <c r="F9" s="0">
+        <v>153.68735716365182</v>
+      </c>
+      <c r="G9" s="0">
+        <v>85142.675758120415</v>
+      </c>
+      <c r="H9" s="0">
+        <v>-8480.8981994427359</v>
+      </c>
+      <c r="I9" s="0">
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="J9" s="0">
+        <v>18.18</v>
+      </c>
+      <c r="K9" s="0">
+        <v>2.4350000000000005</v>
+      </c>
+      <c r="L9" s="0">
+        <v>3.3300000000000001</v>
+      </c>
+      <c r="M9" s="0">
+        <v>225.33371016537902</v>
+      </c>
+      <c r="N9" s="0">
+        <v>6.9702760771831391</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>325</v>
+      </c>
+      <c r="B10" s="0">
+        <v>3339</v>
+      </c>
+      <c r="C10" s="0">
+        <v>325</v>
+      </c>
+      <c r="D10" s="0">
+        <v>59.370829685384848</v>
+      </c>
+      <c r="E10" s="0">
+        <v>480.63999999999999</v>
+      </c>
+      <c r="F10" s="0">
+        <v>153.23650169261165</v>
+      </c>
+      <c r="G10" s="0">
+        <v>81850.623097565796</v>
+      </c>
+      <c r="H10" s="0">
+        <v>-8418.3309107056994</v>
+      </c>
+      <c r="I10" s="0">
+        <v>5.1450000000000005</v>
+      </c>
+      <c r="J10" s="0">
+        <v>18.699999999999999</v>
+      </c>
+      <c r="K10" s="0">
+        <v>2.4299999999999997</v>
+      </c>
+      <c r="L10" s="0">
+        <v>3.3100000000000001</v>
+      </c>
+      <c r="M10" s="0">
+        <v>221.51316105960416</v>
+      </c>
+      <c r="N10" s="0">
+        <v>7.0450677556890939</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>325</v>
+      </c>
+      <c r="B11" s="0">
+        <v>3340</v>
+      </c>
+      <c r="C11" s="0">
+        <v>325</v>
+      </c>
+      <c r="D11" s="0">
+        <v>59.370829685384848</v>
+      </c>
+      <c r="E11" s="0">
+        <v>480.63999999999999</v>
+      </c>
+      <c r="F11" s="0">
+        <v>153.23650169261165</v>
+      </c>
+      <c r="G11" s="0">
+        <v>85024.203600296387</v>
+      </c>
+      <c r="H11" s="0">
+        <v>-8418.3309107056994</v>
+      </c>
+      <c r="I11" s="0">
+        <v>5.1450000000000005</v>
+      </c>
+      <c r="J11" s="0">
+        <v>18.699999999999999</v>
+      </c>
+      <c r="K11" s="0">
+        <v>2.4299999999999997</v>
+      </c>
+      <c r="L11" s="0">
+        <v>3.3100000000000001</v>
+      </c>
+      <c r="M11" s="0">
+        <v>221.51316105960416</v>
+      </c>
+      <c r="N11" s="0">
+        <v>7.0450677556890939</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>325</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3341</v>
+      </c>
+      <c r="C12" s="0">
+        <v>325</v>
+      </c>
+      <c r="D12" s="0">
+        <v>60.017145831727937</v>
+      </c>
+      <c r="E12" s="0">
+        <v>482.34500000000003</v>
+      </c>
+      <c r="F12" s="0">
+        <v>152.69483911626918</v>
+      </c>
+      <c r="G12" s="0">
+        <v>81787.825772647906</v>
+      </c>
+      <c r="H12" s="0">
+        <v>-8343.7672325468611</v>
+      </c>
+      <c r="I12" s="0">
+        <v>5.1150000000000002</v>
+      </c>
+      <c r="J12" s="0">
+        <v>19.375</v>
+      </c>
+      <c r="K12" s="0">
+        <v>2.4300000000000006</v>
+      </c>
+      <c r="L12" s="0">
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="M12" s="0">
+        <v>217.72532881565388</v>
+      </c>
+      <c r="N12" s="0">
+        <v>7.1198327551001013</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>